--- a/data/IKPA_DESEMBER_2024.xlsx
+++ b/data/IKPA_DESEMBER_2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Y68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,20 +541,15 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Uraian Satker-SINGKAT</t>
+          <t>Uraian Satker Final</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Uraian Satker Final</t>
+          <t>Satker</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Satker</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -639,18 +634,17 @@
       <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>BAPAS OKU INDUK</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>BAPAS OKU INDUK (632013)</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
-        <is>
-          <t>BAPAS KELAS II OKU INDUK (632013)</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -742,15 +736,10 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
-        <is>
-          <t>BPS OKU (428258)</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -842,15 +831,10 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
-        <is>
-          <t>PA MARTAPURA (403409)</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -935,18 +919,17 @@
       <c r="V5" t="n">
         <v>4</v>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>RUTAN BATURAJA</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RUMAH TAHANAN NEGARA BATURAJA</t>
+          <t>RUTAN BATURAJA (406472)</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
-        <is>
-          <t>RUMAH TAHANAN NEGARA BATURAJA (406472)</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1031,18 +1014,17 @@
       <c r="V6" t="n">
         <v>5</v>
       </c>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>RUPBASAN BATURAJA</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RUMAH PENYIMPANAN BENDA SITAAN NEGARA BATURAJA</t>
+          <t>RUPBASAN BATURAJA (653271)</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
-        <is>
-          <t>RUMAH PENYIMPANAN BENDA SITAAN NEGARA BATURAJA (653271)</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1134,15 +1116,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
-        <is>
-          <t>POLRES OKUS (665307)</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1234,15 +1211,10 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
-        <is>
-          <t>PA MARTAPURA (401944)</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1334,15 +1306,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
-        <is>
-          <t>KPP BATURAJA (410574)</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1434,15 +1401,10 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440507)</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440507)</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1534,15 +1496,10 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440506)</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1634,15 +1591,10 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
-        <is>
-          <t>MTSN 2 OKUT (418471)</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1734,15 +1686,10 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440504)</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1834,15 +1781,10 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440505)</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -1927,18 +1869,17 @@
       <c r="V15" t="n">
         <v>14</v>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>LAPAS MARTAPURA</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>LAPAS KELAS IIB MUARA DUA</t>
+          <t>LAPAS MARTAPURA (406426)</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
-        <is>
-          <t>LAPAS KELAS IIB MUARA DUA (406426)</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2030,15 +1971,10 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
-        <is>
-          <t>BPS OKUT (668529)</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2130,15 +2066,10 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
-        <is>
-          <t>BPS OKUS (667215)</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2230,15 +2161,10 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
-        <is>
-          <t>POLRES OKUT (665292)</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2330,15 +2256,10 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
-        <is>
-          <t>PA  MUARADUA (403410)</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2430,15 +2351,10 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
-        <is>
-          <t>POLRES OKU (641681)</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2523,18 +2439,17 @@
       <c r="V21" t="n">
         <v>20</v>
       </c>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>LAPAS MARTAPURA</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>LAPAS KELAS IIB MARTAPURA</t>
+          <t>LAPAS MARTAPURA (406488)</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
-        <is>
-          <t>LAPAS KELAS IIB MARTAPURA (406488)</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2626,15 +2541,10 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418456)</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2726,15 +2636,10 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
-        <is>
-          <t>PA BATURAJA (402268)</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2826,15 +2731,10 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
-        <is>
-          <t>BNN OKUT (111079)</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -2926,15 +2826,10 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
-        <is>
-          <t>PA BATURAJA (402267)</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3026,15 +2921,10 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
-        <is>
-          <t>PA MUARADUA (401945)</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3056,7 +2946,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>'098963</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3119,18 +3009,17 @@
       <c r="V27" t="n">
         <v>26</v>
       </c>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PN BATURAJA ('098963)</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
-        <is>
-          <t>PENGADILAN NEGERI BATURAJA (098963)</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3222,15 +3111,10 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666504)</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3322,15 +3206,10 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440503)</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3352,7 +3231,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>'007130</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3415,18 +3294,17 @@
       <c r="V30" t="n">
         <v>29</v>
       </c>
-      <c r="W30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>KEJARI  OKU</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KEJARI  OKU ('007130)</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU (007130)</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3518,15 +3396,10 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
-        <is>
-          <t>MTSN 3 OKUT (553099)</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3618,15 +3491,10 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
-        <is>
-          <t>MAN 2 OKUS (597558)</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3648,7 +3516,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>'099228</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3711,18 +3579,17 @@
       <c r="V33" t="n">
         <v>32</v>
       </c>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>PN BATURAJA</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PN BATURAJA ('099228)</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
-        <is>
-          <t>PENGADILAN NEGERI BATURAJA (099228)</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3809,20 +3676,15 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
-        <is>
-          <t>PUSLATPUR KODIKLATAD (685001)</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -3914,15 +3776,10 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
-        <is>
-          <t>MTSN 4 OKUS (661192)</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4014,15 +3871,10 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKU (426050)</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4114,15 +3966,10 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
-        <is>
-          <t>KPPN BATURAJA (527975)</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4144,7 +3991,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>'007190</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4207,18 +4054,17 @@
       <c r="V38" t="n">
         <v>37</v>
       </c>
-      <c r="W38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>KEJARI OKUT</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>KEJARI OKUT ('007190)</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR (007190)</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4310,15 +4156,10 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666505)</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4410,15 +4251,10 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKUT (424967)</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4510,15 +4346,10 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666503)</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4610,15 +4441,10 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666502)</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4710,15 +4536,10 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666507)</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666507)</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4810,15 +4631,10 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUS (440502)</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -4910,15 +4726,10 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
-        <is>
-          <t>RUMKIT NOESMIR (344894)</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5010,15 +4821,10 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (111071)</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5110,15 +4916,10 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418458)</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5210,15 +5011,10 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418459)</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5310,15 +5106,10 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
-        <is>
-          <t>MTSN 4 OKUT (597480)</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5410,15 +5201,10 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUS (662127)</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5510,15 +5296,10 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
-        <is>
-          <t>KEMENAG OKUT (666501)</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5610,15 +5391,10 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
-        <is>
-          <t>MTSN 1 OKUS (553792)</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5710,15 +5486,10 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
-        <is>
-          <t>MTSN 2 OKUS (418462)</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5810,15 +5581,10 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
-        <is>
-          <t>MAN 1 OKUT (426066)</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -5910,15 +5676,10 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
-        <is>
-          <t>LOKA LABKESMAS (690801)</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6010,15 +5771,10 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418457)</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6110,15 +5866,10 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKU (418461)</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
-        <is>
-          <t>KEMENAG OKU (418461)</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6210,15 +5961,10 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
-        <is>
-          <t>KPU OKUS (656574)</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6310,15 +6056,10 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
-        <is>
-          <t>KPU OKU (656553)</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6410,15 +6151,10 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
-        <is>
-          <t>BAWASLU OKUS (686503)</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6510,15 +6246,10 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
-        <is>
-          <t>BPN OKUS (670561)</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6610,15 +6341,10 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
-        <is>
-          <t>MAN 1 OKU (424245)</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6710,15 +6436,10 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
-        <is>
-          <t>BPN OKU (431142)</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6810,15 +6531,10 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
-        <is>
-          <t>BPN OKUT (669055)</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6910,15 +6626,10 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
-        <is>
-          <t>MTSN 3 OKUS (574370)</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -6940,7 +6651,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>'007208</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7003,18 +6714,17 @@
       <c r="V66" t="n">
         <v>65</v>
       </c>
-      <c r="W66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>KEJARI OKUS</t>
+        </is>
+      </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEJARI OKUS ('007208)</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN (007208)</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -7106,15 +6816,10 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
-        <is>
-          <t>KPU OKUT (656560)</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
@@ -7206,15 +6911,10 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
-        <is>
-          <t>BAWASLU OKU (419006)</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
